--- a/data/outputs/Data_Figure_3.xlsx
+++ b/data/outputs/Data_Figure_3.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\01_3rd_submission\Manuscript_datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\02_Final_revision\0_Final_submission\Manuscript_datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E53FAA-4BE9-430F-84D9-58E62C865100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A2AB1D-9285-4015-A850-BB158D31392E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41520" yWindow="525" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fig 3" sheetId="2" r:id="rId1"/>
+    <sheet name="Figure 3" sheetId="2" r:id="rId1"/>
     <sheet name="REMIND SSP2-RCP2.6" sheetId="1" r:id="rId2"/>
     <sheet name="REMIND SSP1-RCP1.9" sheetId="3" r:id="rId3"/>
     <sheet name="REMIND SSP2-NPi" sheetId="4" r:id="rId4"/>
@@ -23,6 +23,9 @@
     <sheet name="REMIND SPP2-NPi (GDP)" sheetId="8" r:id="rId8"/>
     <sheet name="IMAGE SSP2-RCP2.6 (GDP)" sheetId="9" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -136,25 +139,10 @@
     <t>Ratios to baseline</t>
   </si>
   <si>
-    <t>AESA (FHN allocation) desagregated by fuel type in 2050 with REMIND SSP1-RCP1.9</t>
-  </si>
-  <si>
-    <t>AESA (FHN allocation) desagregated by fuel type in 2050 with REMIND SSP2-Npi</t>
-  </si>
-  <si>
-    <t>AESA (FHN allocation) desagregated by fuel type in 2050 with IMAGE SSP2-RCP2.6</t>
-  </si>
-  <si>
     <t>shares</t>
   </si>
   <si>
-    <t>FHN</t>
-  </si>
-  <si>
     <t>GDP</t>
-  </si>
-  <si>
-    <t>REMIND SSP2-RCP2.6 (GDP)</t>
   </si>
   <si>
     <t>average over Roadmaps</t>
@@ -187,123 +175,43 @@
     <t>avg</t>
   </si>
   <si>
-    <r>
-      <t>AESA (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>FHN allocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>) desagregated by fuel type in 2050 with REMIND SSP2-RCP2.6</t>
-    </r>
+    <t>AESA (ethics-based allocation) desagregated by fuel type in 2050 with REMIND SSP2-RCP2.6</t>
   </si>
   <si>
-    <r>
-      <t>AESA (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>GDP allocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>) desagregated by fuel type in 2050 with REMIND SSP2-RCP2.6</t>
-    </r>
+    <t>AESA (ethics-based allocation) desagregated by fuel type in 2050 with REMIND SSP1-RCP1.9</t>
+  </si>
+  <si>
+    <t>AESA (ethics-based allocation) desagregated by fuel type in 2050 with REMIND SSP2-Npi</t>
+  </si>
+  <si>
+    <t>AESA (ethics-based allocation) desagregated by fuel type in 2050 with IMAGE SSP2-RCP2.6</t>
+  </si>
+  <si>
+    <t>ethics-based</t>
+  </si>
+  <si>
+    <t>AESA (economic-based allocation) desagregated by fuel type in 2050 with REMIND SSP2-RCP2.6</t>
+  </si>
+  <si>
+    <t>AESA (economic-based allocation) desagregated by fuel type in 2050 with REMIND SSP1-RCP1.9</t>
+  </si>
+  <si>
+    <t>AESA (economic-based allocation) desagregated by fuel type in 2050 with REMIND SSP2-Npi</t>
+  </si>
+  <si>
+    <t>AESA (economic-based allocation) desagregated by fuel type in 2050 with IMAGE SSP2-RCP2.6</t>
+  </si>
+  <si>
+    <t>REMIND SSP2-RCP2.6 (GDP)</t>
   </si>
   <si>
     <t>REMIND SSP1-RCP1.9 (GDP)</t>
   </si>
   <si>
-    <t>IMAGE SSP2-RCP2.6 (GDP)</t>
-  </si>
-  <si>
-    <r>
-      <t>AESA (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>GDP allocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>) desagregated by fuel type in 2050 with REMIND SSP1-RCP1.9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>AESA (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>GDP allocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>) desagregated by fuel type in 2050 with IMAGE SSP2-RCP2.6</t>
-    </r>
-  </si>
-  <si>
     <t>REMIND SSP2-NPi (GDP)</t>
   </si>
   <si>
-    <r>
-      <t>AESA (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>GDP allocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>) desagregated by fuel type in 2050 with REMIND SSP2-Npi</t>
-    </r>
+    <t>IMAGE SSP2-RCP2.6 (GDP)</t>
   </si>
 </sst>
 </file>
@@ -313,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,11 +262,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -663,6 +566,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -689,9 +595,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1002,6 +905,19 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="REMIND SSP2-RCP2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1286,7 +1202,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1294,7 +1210,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1302,7 +1218,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1310,23 +1226,23 @@
         <v>20</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1334,15 +1250,15 @@
         <v>53</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1384,17 +1300,17 @@
       <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1438,7 +1354,7 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1463,33 +1379,33 @@
       <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="29">
         <f>C17/C9</f>
         <v>0.92103319538740624</v>
       </c>
-      <c r="L3" s="38">
-        <f t="shared" ref="K3:P3" si="0">D17/D9</f>
+      <c r="L3" s="29">
+        <f t="shared" ref="L3:P3" si="0">D17/D9</f>
         <v>1.2820593085792942</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="29">
         <f t="shared" si="0"/>
         <v>5.6913815831320056</v>
       </c>
-      <c r="N3" s="38">
+      <c r="N3" s="29">
         <f t="shared" si="0"/>
         <v>6.6704607343009084</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3" s="29">
         <f t="shared" si="0"/>
         <v>5.5296665970013361</v>
       </c>
-      <c r="P3" s="38">
+      <c r="P3" s="29">
         <f t="shared" si="0"/>
         <v>1.5383400436559223</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1514,33 +1430,33 @@
       <c r="J4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="29">
         <f>C25/C9</f>
         <v>0.74249458750375041</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="29">
         <f>D25/D9</f>
         <v>1.7549149447598973</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="29">
         <f>E25/E9</f>
         <v>13.297707522786734</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="29">
         <f>F25/F9</f>
         <v>16.803399541350995</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="29">
         <f>G25/G9</f>
         <v>12.577169393743427</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="29">
         <f t="shared" ref="P4" si="1">H25/H9</f>
         <v>2.5284198168778587</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1565,33 +1481,33 @@
       <c r="J5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="38">
+      <c r="K5" s="29">
         <f>C33/C9</f>
         <v>0.61367521658597268</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="29">
         <f>D33/D9</f>
         <v>1.5490499556701096</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="29">
         <f>E33/E9</f>
         <v>19.871442015804849</v>
       </c>
-      <c r="N5" s="38">
+      <c r="N5" s="29">
         <f>F33/F9</f>
         <v>16.444805093690338</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5" s="29">
         <f>G33/G9</f>
         <v>21.126568454091693</v>
       </c>
-      <c r="P5" s="38">
+      <c r="P5" s="29">
         <f t="shared" ref="P5" si="2">H33/H9</f>
         <v>2.2264248802361011</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1616,33 +1532,33 @@
       <c r="J6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="29">
         <f>C41/C9</f>
         <v>0.7737652412984023</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="29">
         <f>D41/D9</f>
         <v>1.5228033483446022</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="29">
         <f>E41/E9</f>
         <v>13.913331993043665</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="29">
         <f>F41/F9</f>
         <v>13.083277409675839</v>
       </c>
-      <c r="O6" s="38">
+      <c r="O6" s="29">
         <f>G41/G9</f>
         <v>14.581523523271755</v>
       </c>
-      <c r="P6" s="38">
+      <c r="P6" s="29">
         <f t="shared" ref="P6" si="3">H41/H9</f>
         <v>2.0417559730124579</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1667,33 +1583,33 @@
       <c r="J7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="29">
         <f>C49/C9</f>
         <v>0.41853820411494386</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="29">
         <f>D49/D9</f>
         <v>2.1927515736571093</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="29">
         <f>E49/E9</f>
         <v>16.470489912266672</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="29">
         <f>F49/F9</f>
         <v>28.027915229854436</v>
       </c>
-      <c r="O7" s="38">
+      <c r="O7" s="29">
         <f>G49/G9</f>
         <v>13.306708772186939</v>
       </c>
-      <c r="P7" s="38">
+      <c r="P7" s="29">
         <f t="shared" ref="P7" si="4">H49/H9</f>
         <v>3.8150036558227725</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -1718,33 +1634,33 @@
       <c r="J8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="29">
         <f>C57/C9</f>
         <v>0.60776076983619409</v>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="29">
         <f>D57/D9</f>
         <v>1.2777371718957664</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="29">
         <f>E57/E9</f>
         <v>27.888913700695873</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="29">
         <f>F57/F9</f>
         <v>38.728581111984077</v>
       </c>
-      <c r="O8" s="38">
+      <c r="O8" s="29">
         <f>G57/G9</f>
         <v>15.570347777992495</v>
       </c>
-      <c r="P8" s="38">
+      <c r="P8" s="29">
         <f t="shared" ref="P8" si="5">H57/H9</f>
         <v>6.3797537737319203</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1775,33 +1691,33 @@
       <c r="J9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="29">
         <f>C65/C9</f>
         <v>0.8695177297180865</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9" s="29">
         <f>D65/D9</f>
         <v>1.2161517873531762</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="29">
         <f>E65/E9</f>
         <v>22.072826964885401</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="29">
         <f>F65/F9</f>
         <v>8.1664379807797403</v>
       </c>
-      <c r="O9" s="38">
+      <c r="O9" s="29">
         <f>G65/G9</f>
         <v>27.127517038221733</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="29">
         <f t="shared" ref="P9" si="7">H65/H9</f>
         <v>1.1330517841649705</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1830,33 +1746,33 @@
       <c r="J10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="29">
         <f>C73/C9</f>
         <v>0.70881057761592736</v>
       </c>
-      <c r="L10" s="38">
+      <c r="L10" s="29">
         <f>D73/D9</f>
         <v>1.0646553354852943</v>
       </c>
-      <c r="M10" s="38">
+      <c r="M10" s="29">
         <f>E73/E9</f>
         <v>25.12131927706362</v>
       </c>
-      <c r="N10" s="38">
+      <c r="N10" s="29">
         <f>F73/F9</f>
         <v>11.965254517579826</v>
       </c>
-      <c r="O10" s="38">
+      <c r="O10" s="29">
         <f>G73/G9</f>
         <v>11.730952441602321</v>
       </c>
-      <c r="P10" s="38">
+      <c r="P10" s="29">
         <f t="shared" ref="P10" si="8">H73/H9</f>
         <v>1.1332429059334836</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1879,7 +1795,7 @@
         <v>5.5614099645469109E-2</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K11" s="7">
         <f>AVERAGE(K3:K6)</f>
@@ -1907,7 +1823,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -1930,7 +1846,7 @@
         <v>7.2893338226377152E-3</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K12" s="21">
         <f>K4/K6-1</f>
@@ -1957,7 +1873,7 @@
         <v>0.23835553822201616</v>
       </c>
       <c r="Q12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R12" s="20">
         <f>AVERAGE(L12:P12)</f>
@@ -1965,7 +1881,7 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
@@ -1988,7 +1904,7 @@
         <v>2.4180562976351069E-2</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K13" s="21">
         <f>K9/K10-1</f>
@@ -2016,7 +1932,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -2038,18 +1954,18 @@
       <c r="H14" s="4">
         <v>1.346369179991368E-2</v>
       </c>
-      <c r="J14" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
+      <c r="J14" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -2072,7 +1988,7 @@
         <v>1.6616742311777351E-2</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K15" s="23">
         <f>'REMIND SSP1-RCP1.9'!C65/'REMIND SSP2-RCP2.6'!C65</f>
@@ -2100,7 +2016,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
@@ -2123,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K16" s="23">
         <f>'REMIND SSP2-NPi'!C65/'REMIND SSP2-RCP2.6'!C65</f>
@@ -2151,7 +2067,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
@@ -2180,7 +2096,7 @@
         <v>0.11716443055614892</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K17" s="23">
         <f>'IMAGE SSP2-RCP2.6'!C65/'REMIND SSP2-RCP2.6'!C65</f>
@@ -2208,7 +2124,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2235,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K18" s="18">
         <f>AVERAGE(K15:K17)</f>
@@ -2267,7 +2183,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -2289,18 +2205,18 @@
       <c r="H19" s="4">
         <v>2.143216588029075E-2</v>
       </c>
-      <c r="J19" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
+      <c r="J19" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
@@ -2323,7 +2239,7 @@
         <v>1.6397229418458881E-2</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K20" s="7">
         <f>'REMIND SSP1-RCP1.9'!C73/'REMIND SSP2-RCP2.6'!C73</f>
@@ -2351,7 +2267,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -2374,7 +2290,7 @@
         <v>6.8958515034030762E-2</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K21" s="7">
         <f>'REMIND SSP2-NPi'!C73/'REMIND SSP2-RCP2.6'!C73</f>
@@ -2402,7 +2318,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -2425,7 +2341,7 @@
         <v>3.8395970941864657E-2</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K22" s="7">
         <f>'IMAGE SSP2-RCP2.6'!C73/'REMIND SSP2-RCP2.6'!C73</f>
@@ -2453,7 +2369,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
         <v>13</v>
       </c>
@@ -2476,7 +2392,7 @@
         <v>4.738789066424906E-2</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K23" s="18">
         <f>AVERAGE(K20:K22)</f>
@@ -2508,7 +2424,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -2532,7 +2448,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
@@ -2562,7 +2478,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -2590,7 +2506,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
@@ -2614,7 +2530,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -2638,7 +2554,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="3" t="s">
         <v>11</v>
       </c>
@@ -2662,7 +2578,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -2686,7 +2602,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
@@ -2710,7 +2626,7 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
@@ -2734,7 +2650,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
@@ -2764,7 +2680,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -2792,7 +2708,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
@@ -2816,7 +2732,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
@@ -2840,7 +2756,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="3" t="s">
         <v>11</v>
       </c>
@@ -2864,7 +2780,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -2888,7 +2804,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
@@ -2912,7 +2828,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="3" t="s">
         <v>14</v>
       </c>
@@ -2936,7 +2852,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="3" t="s">
         <v>15</v>
       </c>
@@ -2966,7 +2882,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -2994,7 +2910,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
@@ -3018,7 +2934,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="3" t="s">
         <v>10</v>
       </c>
@@ -3042,7 +2958,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="3" t="s">
         <v>11</v>
       </c>
@@ -3066,7 +2982,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3090,7 +3006,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
@@ -3114,7 +3030,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="3" t="s">
         <v>14</v>
       </c>
@@ -3138,7 +3054,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
@@ -3168,7 +3084,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -3196,7 +3112,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="3" t="s">
         <v>9</v>
       </c>
@@ -3220,7 +3136,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="3" t="s">
         <v>10</v>
       </c>
@@ -3244,7 +3160,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
@@ -3268,7 +3184,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -3292,7 +3208,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="3" t="s">
         <v>13</v>
       </c>
@@ -3316,7 +3232,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="3" t="s">
         <v>14</v>
       </c>
@@ -3340,7 +3256,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="3" t="s">
         <v>15</v>
       </c>
@@ -3370,7 +3286,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3398,7 +3314,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="3" t="s">
         <v>9</v>
       </c>
@@ -3422,7 +3338,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3446,7 +3362,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="3" t="s">
         <v>11</v>
       </c>
@@ -3470,7 +3386,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="3" t="s">
         <v>12</v>
       </c>
@@ -3494,7 +3410,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="3" t="s">
         <v>13</v>
       </c>
@@ -3518,7 +3434,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="3" t="s">
         <v>14</v>
       </c>
@@ -3542,7 +3458,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="3" t="s">
         <v>15</v>
       </c>
@@ -3572,7 +3488,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -3600,7 +3516,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
@@ -3624,7 +3540,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="3" t="s">
         <v>10</v>
       </c>
@@ -3648,7 +3564,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="3" t="s">
         <v>11</v>
       </c>
@@ -3672,7 +3588,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="3" t="s">
         <v>12</v>
       </c>
@@ -3696,7 +3612,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="3" t="s">
         <v>13</v>
       </c>
@@ -3720,7 +3636,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="3" t="s">
         <v>14</v>
       </c>
@@ -3744,7 +3660,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="3" t="s">
         <v>15</v>
       </c>
@@ -3823,17 +3739,17 @@
       <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="35"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3877,7 +3793,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -3928,7 +3844,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -3979,7 +3895,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -4030,7 +3946,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -4081,7 +3997,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -4132,7 +4048,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -4183,7 +4099,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -4234,7 +4150,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -4287,7 +4203,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -4311,7 +4227,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4335,7 +4251,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
@@ -4359,7 +4275,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -4383,7 +4299,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -4407,7 +4323,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
@@ -4431,7 +4347,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
@@ -4455,7 +4371,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -4481,7 +4397,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -4505,7 +4421,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
@@ -4529,7 +4445,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -4553,7 +4469,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -4577,7 +4493,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
         <v>13</v>
       </c>
@@ -4601,7 +4517,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -4625,7 +4541,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
@@ -4649,7 +4565,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -4675,7 +4591,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
@@ -4699,7 +4615,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -4723,7 +4639,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="3" t="s">
         <v>11</v>
       </c>
@@ -4747,7 +4663,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -4771,7 +4687,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
@@ -4795,7 +4711,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
@@ -4819,7 +4735,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
@@ -4843,7 +4759,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -4869,7 +4785,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
@@ -4893,7 +4809,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
@@ -4917,7 +4833,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="3" t="s">
         <v>11</v>
       </c>
@@ -4941,7 +4857,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -4965,7 +4881,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
@@ -4989,7 +4905,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="3" t="s">
         <v>14</v>
       </c>
@@ -5013,7 +4929,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="3" t="s">
         <v>15</v>
       </c>
@@ -5037,7 +4953,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -5063,7 +4979,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
@@ -5087,7 +5003,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="3" t="s">
         <v>10</v>
       </c>
@@ -5111,7 +5027,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="3" t="s">
         <v>11</v>
       </c>
@@ -5135,7 +5051,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
@@ -5159,7 +5075,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
@@ -5183,7 +5099,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="3" t="s">
         <v>14</v>
       </c>
@@ -5207,7 +5123,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
@@ -5231,7 +5147,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -5257,7 +5173,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="3" t="s">
         <v>9</v>
       </c>
@@ -5281,7 +5197,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="3" t="s">
         <v>10</v>
       </c>
@@ -5305,7 +5221,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
@@ -5329,7 +5245,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -5353,7 +5269,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="3" t="s">
         <v>13</v>
       </c>
@@ -5377,7 +5293,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="3" t="s">
         <v>14</v>
       </c>
@@ -5401,7 +5317,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="3" t="s">
         <v>15</v>
       </c>
@@ -5425,7 +5341,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -5451,7 +5367,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="3" t="s">
         <v>9</v>
       </c>
@@ -5475,7 +5391,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -5499,7 +5415,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="3" t="s">
         <v>11</v>
       </c>
@@ -5523,7 +5439,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="3" t="s">
         <v>12</v>
       </c>
@@ -5547,7 +5463,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="3" t="s">
         <v>13</v>
       </c>
@@ -5571,7 +5487,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="3" t="s">
         <v>14</v>
       </c>
@@ -5595,7 +5511,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="3" t="s">
         <v>15</v>
       </c>
@@ -5619,7 +5535,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -5645,7 +5561,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
@@ -5669,7 +5585,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="3" t="s">
         <v>10</v>
       </c>
@@ -5693,7 +5609,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="3" t="s">
         <v>11</v>
       </c>
@@ -5717,7 +5633,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="3" t="s">
         <v>12</v>
       </c>
@@ -5741,7 +5657,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="3" t="s">
         <v>13</v>
       </c>
@@ -5765,7 +5681,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="3" t="s">
         <v>14</v>
       </c>
@@ -5789,7 +5705,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="3" t="s">
         <v>15</v>
       </c>
@@ -5860,17 +5776,17 @@
         <v>6</v>
       </c>
       <c r="J1" s="8"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="38"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -5915,7 +5831,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -5960,7 +5876,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -6005,7 +5921,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -6050,7 +5966,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -6095,7 +6011,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -6140,7 +6056,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -6185,7 +6101,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -6230,7 +6146,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -6277,7 +6193,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -6301,7 +6217,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -6325,7 +6241,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
@@ -6349,7 +6265,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -6373,7 +6289,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -6397,7 +6313,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
@@ -6421,7 +6337,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
@@ -6445,7 +6361,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -6471,7 +6387,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -6495,7 +6411,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
@@ -6519,7 +6435,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -6543,7 +6459,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -6567,7 +6483,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
         <v>13</v>
       </c>
@@ -6591,7 +6507,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -6615,7 +6531,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
@@ -6639,7 +6555,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -6665,7 +6581,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
@@ -6689,7 +6605,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -6713,7 +6629,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="3" t="s">
         <v>11</v>
       </c>
@@ -6737,7 +6653,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -6761,7 +6677,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
@@ -6785,7 +6701,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
@@ -6809,7 +6725,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
@@ -6833,7 +6749,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -6859,7 +6775,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
@@ -6883,7 +6799,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
@@ -6907,7 +6823,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="3" t="s">
         <v>11</v>
       </c>
@@ -6931,7 +6847,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -6955,7 +6871,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
@@ -6979,7 +6895,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="3" t="s">
         <v>14</v>
       </c>
@@ -7003,7 +6919,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="3" t="s">
         <v>15</v>
       </c>
@@ -7027,7 +6943,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -7053,7 +6969,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
@@ -7077,7 +6993,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="3" t="s">
         <v>10</v>
       </c>
@@ -7101,7 +7017,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="3" t="s">
         <v>11</v>
       </c>
@@ -7125,7 +7041,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
@@ -7149,7 +7065,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
@@ -7173,7 +7089,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="3" t="s">
         <v>14</v>
       </c>
@@ -7197,7 +7113,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
@@ -7221,7 +7137,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -7247,7 +7163,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="3" t="s">
         <v>9</v>
       </c>
@@ -7271,7 +7187,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="3" t="s">
         <v>10</v>
       </c>
@@ -7295,7 +7211,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
@@ -7319,7 +7235,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -7343,7 +7259,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="3" t="s">
         <v>13</v>
       </c>
@@ -7367,7 +7283,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="3" t="s">
         <v>14</v>
       </c>
@@ -7391,7 +7307,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="3" t="s">
         <v>15</v>
       </c>
@@ -7415,7 +7331,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -7441,7 +7357,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="3" t="s">
         <v>9</v>
       </c>
@@ -7465,7 +7381,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -7489,7 +7405,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="3" t="s">
         <v>11</v>
       </c>
@@ -7513,7 +7429,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="3" t="s">
         <v>12</v>
       </c>
@@ -7537,7 +7453,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="3" t="s">
         <v>13</v>
       </c>
@@ -7561,7 +7477,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="3" t="s">
         <v>14</v>
       </c>
@@ -7585,7 +7501,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="3" t="s">
         <v>15</v>
       </c>
@@ -7609,7 +7525,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -7635,7 +7551,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
@@ -7659,7 +7575,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="3" t="s">
         <v>10</v>
       </c>
@@ -7683,7 +7599,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="3" t="s">
         <v>11</v>
       </c>
@@ -7707,7 +7623,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="3" t="s">
         <v>12</v>
       </c>
@@ -7731,7 +7647,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="3" t="s">
         <v>13</v>
       </c>
@@ -7755,7 +7671,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="3" t="s">
         <v>14</v>
       </c>
@@ -7779,7 +7695,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="3" t="s">
         <v>15</v>
       </c>
@@ -7850,17 +7766,17 @@
         <v>6</v>
       </c>
       <c r="J1" s="8"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="38"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -7905,7 +7821,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -7950,7 +7866,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -7995,7 +7911,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -8040,7 +7956,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -8085,7 +8001,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -8130,7 +8046,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -8175,7 +8091,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -8220,7 +8136,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -8267,7 +8183,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -8291,7 +8207,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -8315,7 +8231,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
@@ -8339,7 +8255,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -8363,7 +8279,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -8387,7 +8303,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
@@ -8411,7 +8327,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
@@ -8435,7 +8351,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -8461,7 +8377,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -8485,7 +8401,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
@@ -8509,7 +8425,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -8533,7 +8449,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -8557,7 +8473,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
         <v>13</v>
       </c>
@@ -8581,7 +8497,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -8605,7 +8521,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
@@ -8629,7 +8545,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -8655,7 +8571,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
@@ -8679,7 +8595,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -8703,7 +8619,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="3" t="s">
         <v>11</v>
       </c>
@@ -8727,7 +8643,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -8751,7 +8667,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
@@ -8775,7 +8691,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
@@ -8799,7 +8715,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
@@ -8823,7 +8739,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -8849,7 +8765,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
@@ -8873,7 +8789,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
@@ -8897,7 +8813,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="3" t="s">
         <v>11</v>
       </c>
@@ -8921,7 +8837,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -8945,7 +8861,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
@@ -8969,7 +8885,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="3" t="s">
         <v>14</v>
       </c>
@@ -8993,7 +8909,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="3" t="s">
         <v>15</v>
       </c>
@@ -9017,7 +8933,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -9043,7 +8959,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
@@ -9067,7 +8983,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="3" t="s">
         <v>10</v>
       </c>
@@ -9091,7 +9007,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="3" t="s">
         <v>11</v>
       </c>
@@ -9115,7 +9031,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
@@ -9139,7 +9055,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
@@ -9163,7 +9079,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="3" t="s">
         <v>14</v>
       </c>
@@ -9187,7 +9103,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
@@ -9211,7 +9127,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -9237,7 +9153,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="3" t="s">
         <v>9</v>
       </c>
@@ -9261,7 +9177,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="3" t="s">
         <v>10</v>
       </c>
@@ -9285,7 +9201,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
@@ -9309,7 +9225,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -9333,7 +9249,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="3" t="s">
         <v>13</v>
       </c>
@@ -9357,7 +9273,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="3" t="s">
         <v>14</v>
       </c>
@@ -9381,7 +9297,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="3" t="s">
         <v>15</v>
       </c>
@@ -9405,7 +9321,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -9431,7 +9347,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="3" t="s">
         <v>9</v>
       </c>
@@ -9455,7 +9371,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -9479,7 +9395,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="3" t="s">
         <v>11</v>
       </c>
@@ -9503,7 +9419,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="3" t="s">
         <v>12</v>
       </c>
@@ -9527,7 +9443,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="3" t="s">
         <v>13</v>
       </c>
@@ -9551,7 +9467,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="3" t="s">
         <v>14</v>
       </c>
@@ -9575,7 +9491,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="3" t="s">
         <v>15</v>
       </c>
@@ -9599,7 +9515,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -9625,7 +9541,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
@@ -9649,7 +9565,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="3" t="s">
         <v>10</v>
       </c>
@@ -9673,7 +9589,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="3" t="s">
         <v>11</v>
       </c>
@@ -9697,7 +9613,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="3" t="s">
         <v>12</v>
       </c>
@@ -9721,7 +9637,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="3" t="s">
         <v>13</v>
       </c>
@@ -9745,7 +9661,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="3" t="s">
         <v>14</v>
       </c>
@@ -9769,7 +9685,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="3" t="s">
         <v>15</v>
       </c>
@@ -9843,29 +9759,29 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4">
-        <f>'REMIND SSP2-RCP2.6'!C2/'REMIND SSP2-RCP2.6 (GDP)'!K$14*'REMIND SSP2-RCP2.6 (GDP)'!K$13</f>
-        <v>1.0332829962259993</v>
-      </c>
-      <c r="D2" s="4">
-        <f>'REMIND SSP2-RCP2.6'!D2/'REMIND SSP2-RCP2.6 (GDP)'!L$14*'REMIND SSP2-RCP2.6 (GDP)'!L$13</f>
-        <v>0.5200997440466768</v>
+      <c r="C2" s="4" t="e">
+        <f>'REMIND SSP2-RCP2.6'!C2/'[1]REMIND SSP2-RCP2'!K$14*'[1]REMIND SSP2-RCP2'!K$13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D2" s="4" t="e">
+        <f>'REMIND SSP2-RCP2.6'!D2/'[1]REMIND SSP2-RCP2'!L$14*'[1]REMIND SSP2-RCP2'!L$13</f>
+        <v>#REF!</v>
       </c>
       <c r="E2" s="4">
         <f>'REMIND SSP2-RCP2.6'!E2/'REMIND SSP2-RCP2.6 (GDP)'!M$14*'REMIND SSP2-RCP2.6 (GDP)'!M$13</f>
@@ -9903,7 +9819,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -9960,7 +9876,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -10017,7 +9933,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -10074,7 +9990,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -10131,7 +10047,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -10188,7 +10104,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -10245,7 +10161,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -10302,7 +10218,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -10361,7 +10277,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -10391,7 +10307,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
@@ -10420,7 +10336,7 @@
         <v>1.0054253548465815E-3</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>2</v>
@@ -10442,7 +10358,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
@@ -10471,7 +10387,7 @@
         <v>3.3352500657035963E-3</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K13" s="15">
         <v>0.9</v>
@@ -10493,7 +10409,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -10522,7 +10438,7 @@
         <v>1.8570609379191284E-3</v>
       </c>
       <c r="J14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K14" s="15">
         <v>2.9</v>
@@ -10544,7 +10460,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -10574,7 +10490,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
@@ -10604,7 +10520,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
@@ -10634,7 +10550,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -10666,7 +10582,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -10696,7 +10612,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
@@ -10726,7 +10642,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -10756,7 +10672,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -10786,7 +10702,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
         <v>13</v>
       </c>
@@ -10816,7 +10732,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -10846,7 +10762,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
         <v>15</v>
       </c>
@@ -10876,7 +10792,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -10908,7 +10824,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
@@ -10938,7 +10854,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -10968,7 +10884,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="3" t="s">
         <v>11</v>
       </c>
@@ -10998,7 +10914,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -11028,7 +10944,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="3" t="s">
         <v>13</v>
       </c>
@@ -11058,7 +10974,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
@@ -11088,7 +11004,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
@@ -11118,7 +11034,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -11150,7 +11066,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
@@ -11180,7 +11096,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
@@ -11210,7 +11126,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="3" t="s">
         <v>11</v>
       </c>
@@ -11240,7 +11156,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -11270,7 +11186,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
@@ -11300,7 +11216,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="3" t="s">
         <v>14</v>
       </c>
@@ -11330,7 +11246,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="3" t="s">
         <v>15</v>
       </c>
@@ -11360,7 +11276,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -11392,7 +11308,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
@@ -11422,7 +11338,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="3" t="s">
         <v>10</v>
       </c>
@@ -11452,7 +11368,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="3" t="s">
         <v>11</v>
       </c>
@@ -11482,7 +11398,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
@@ -11512,7 +11428,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
@@ -11542,7 +11458,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="3" t="s">
         <v>14</v>
       </c>
@@ -11572,7 +11488,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
@@ -11602,7 +11518,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -11634,7 +11550,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="3" t="s">
         <v>9</v>
       </c>
@@ -11664,7 +11580,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="3" t="s">
         <v>10</v>
       </c>
@@ -11694,7 +11610,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
@@ -11724,7 +11640,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -11754,7 +11670,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="3" t="s">
         <v>13</v>
       </c>
@@ -11784,7 +11700,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="3" t="s">
         <v>14</v>
       </c>
@@ -11814,7 +11730,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="3" t="s">
         <v>15</v>
       </c>
@@ -11844,7 +11760,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -11876,7 +11792,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="3" t="s">
         <v>9</v>
       </c>
@@ -11906,7 +11822,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -11936,7 +11852,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="3" t="s">
         <v>11</v>
       </c>
@@ -11966,7 +11882,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="3" t="s">
         <v>12</v>
       </c>
@@ -11996,7 +11912,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="3" t="s">
         <v>13</v>
       </c>
@@ -12026,7 +11942,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="3" t="s">
         <v>14</v>
       </c>
@@ -12056,7 +11972,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="3" t="s">
         <v>15</v>
       </c>
@@ -12086,7 +12002,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -12118,7 +12034,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
@@ -12148,7 +12064,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="3" t="s">
         <v>10</v>
       </c>
@@ -12178,7 +12094,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="3" t="s">
         <v>11</v>
       </c>
@@ -12208,7 +12124,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="3" t="s">
         <v>12</v>
       </c>
@@ -12238,7 +12154,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="3" t="s">
         <v>13</v>
       </c>
@@ -12268,7 +12184,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="3" t="s">
         <v>14</v>
       </c>
@@ -12298,7 +12214,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="3" t="s">
         <v>15</v>
       </c>
@@ -12368,17 +12284,17 @@
       <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -12428,7 +12344,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
@@ -12485,7 +12401,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="24" t="s">
         <v>10</v>
       </c>
@@ -12542,7 +12458,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
       </c>
@@ -12599,7 +12515,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
@@ -12656,7 +12572,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="24" t="s">
         <v>13</v>
       </c>
@@ -12713,7 +12629,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="24" t="s">
         <v>14</v>
       </c>
@@ -12770,7 +12686,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="24" t="s">
         <v>15</v>
       </c>
@@ -12827,7 +12743,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="24" t="s">
@@ -12886,7 +12802,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="24" t="s">
         <v>9</v>
       </c>
@@ -12916,7 +12832,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="24" t="s">
         <v>10</v>
       </c>
@@ -12945,7 +12861,7 @@
         <v>1.0213122045495634E-3</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>2</v>
@@ -12967,7 +12883,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="24" t="s">
         <v>11</v>
       </c>
@@ -12996,7 +12912,7 @@
         <v>1.9132621153453103E-3</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K13" s="15">
         <v>0.9</v>
@@ -13018,7 +12934,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
@@ -13047,7 +12963,7 @@
         <v>1.9403710150441202E-3</v>
       </c>
       <c r="J14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K14" s="15">
         <v>2.9</v>
@@ -13069,7 +12985,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="24" t="s">
         <v>13</v>
       </c>
@@ -13099,7 +13015,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="24" t="s">
         <v>14</v>
       </c>
@@ -13129,7 +13045,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="24" t="s">
         <v>15</v>
       </c>
@@ -13159,7 +13075,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="24" t="s">
@@ -13191,7 +13107,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="24" t="s">
         <v>9</v>
       </c>
@@ -13221,7 +13137,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="24" t="s">
         <v>10</v>
       </c>
@@ -13251,7 +13167,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="24" t="s">
         <v>11</v>
       </c>
@@ -13281,7 +13197,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="24" t="s">
         <v>12</v>
       </c>
@@ -13311,7 +13227,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="24" t="s">
         <v>13</v>
       </c>
@@ -13341,7 +13257,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="24" t="s">
         <v>14</v>
       </c>
@@ -13371,7 +13287,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="24" t="s">
         <v>15</v>
       </c>
@@ -13401,7 +13317,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="24" t="s">
@@ -13433,7 +13349,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="24" t="s">
         <v>9</v>
       </c>
@@ -13463,7 +13379,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="24" t="s">
         <v>10</v>
       </c>
@@ -13493,7 +13409,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="24" t="s">
         <v>11</v>
       </c>
@@ -13523,7 +13439,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="24" t="s">
         <v>12</v>
       </c>
@@ -13553,7 +13469,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="24" t="s">
         <v>13</v>
       </c>
@@ -13583,7 +13499,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="24" t="s">
         <v>14</v>
       </c>
@@ -13613,7 +13529,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="24" t="s">
         <v>15</v>
       </c>
@@ -13643,7 +13559,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
@@ -13675,7 +13591,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="24" t="s">
         <v>9</v>
       </c>
@@ -13705,7 +13621,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="24" t="s">
         <v>10</v>
       </c>
@@ -13735,7 +13651,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="24" t="s">
         <v>11</v>
       </c>
@@ -13765,7 +13681,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="24" t="s">
         <v>12</v>
       </c>
@@ -13795,7 +13711,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="24" t="s">
         <v>13</v>
       </c>
@@ -13825,7 +13741,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="24" t="s">
         <v>14</v>
       </c>
@@ -13855,7 +13771,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="24" t="s">
         <v>15</v>
       </c>
@@ -13885,7 +13801,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="24" t="s">
@@ -13917,7 +13833,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="24" t="s">
         <v>9</v>
       </c>
@@ -13947,7 +13863,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="24" t="s">
         <v>10</v>
       </c>
@@ -13977,7 +13893,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="24" t="s">
         <v>11</v>
       </c>
@@ -14007,7 +13923,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="24" t="s">
         <v>12</v>
       </c>
@@ -14037,7 +13953,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="24" t="s">
         <v>13</v>
       </c>
@@ -14067,7 +13983,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="24" t="s">
         <v>14</v>
       </c>
@@ -14097,7 +14013,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="24" t="s">
         <v>15</v>
       </c>
@@ -14127,7 +14043,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="24" t="s">
@@ -14159,7 +14075,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="24" t="s">
         <v>9</v>
       </c>
@@ -14189,7 +14105,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="24" t="s">
         <v>10</v>
       </c>
@@ -14219,7 +14135,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="24" t="s">
         <v>11</v>
       </c>
@@ -14249,7 +14165,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="24" t="s">
         <v>12</v>
       </c>
@@ -14279,7 +14195,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="24" t="s">
         <v>13</v>
       </c>
@@ -14309,7 +14225,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="24" t="s">
         <v>14</v>
       </c>
@@ -14339,7 +14255,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="24" t="s">
         <v>15</v>
       </c>
@@ -14369,7 +14285,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="24" t="s">
@@ -14401,7 +14317,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="24" t="s">
         <v>9</v>
       </c>
@@ -14431,7 +14347,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="24" t="s">
         <v>10</v>
       </c>
@@ -14461,7 +14377,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="24" t="s">
         <v>11</v>
       </c>
@@ -14491,7 +14407,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="24" t="s">
         <v>12</v>
       </c>
@@ -14521,7 +14437,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="24" t="s">
         <v>13</v>
       </c>
@@ -14551,7 +14467,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="24" t="s">
         <v>14</v>
       </c>
@@ -14581,7 +14497,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="24" t="s">
         <v>15</v>
       </c>
@@ -14611,7 +14527,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="24" t="s">
@@ -14643,7 +14559,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="24" t="s">
         <v>9</v>
       </c>
@@ -14673,7 +14589,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="24" t="s">
         <v>10</v>
       </c>
@@ -14703,7 +14619,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="24" t="s">
         <v>11</v>
       </c>
@@ -14733,7 +14649,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="24" t="s">
         <v>12</v>
       </c>
@@ -14763,7 +14679,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="24" t="s">
         <v>13</v>
       </c>
@@ -14793,7 +14709,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="24" t="s">
         <v>14</v>
       </c>
@@ -14823,7 +14739,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="24" t="s">
         <v>15</v>
       </c>
@@ -14893,17 +14809,17 @@
       <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -14953,7 +14869,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
@@ -15010,7 +14926,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="24" t="s">
         <v>10</v>
       </c>
@@ -15067,7 +14983,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
       </c>
@@ -15124,7 +15040,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
@@ -15181,7 +15097,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="24" t="s">
         <v>13</v>
       </c>
@@ -15238,7 +15154,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="24" t="s">
         <v>14</v>
       </c>
@@ -15295,7 +15211,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="24" t="s">
         <v>15</v>
       </c>
@@ -15352,7 +15268,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="24" t="s">
@@ -15411,7 +15327,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="24" t="s">
         <v>9</v>
       </c>
@@ -15441,7 +15357,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="24" t="s">
         <v>10</v>
       </c>
@@ -15470,7 +15386,7 @@
         <v>1.4331733983840443E-3</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>2</v>
@@ -15492,7 +15408,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="24" t="s">
         <v>11</v>
       </c>
@@ -15521,7 +15437,7 @@
         <v>1.892844413593592E-3</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K13" s="15">
         <v>0.9</v>
@@ -15543,7 +15459,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
@@ -15572,7 +15488,7 @@
         <v>1.832467593720858E-3</v>
       </c>
       <c r="J14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K14" s="15">
         <v>2.9</v>
@@ -15594,7 +15510,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="24" t="s">
         <v>13</v>
       </c>
@@ -15624,7 +15540,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="24" t="s">
         <v>14</v>
       </c>
@@ -15654,7 +15570,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="24" t="s">
         <v>15</v>
       </c>
@@ -15684,7 +15600,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="24" t="s">
@@ -15716,7 +15632,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="24" t="s">
         <v>9</v>
       </c>
@@ -15746,7 +15662,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="24" t="s">
         <v>10</v>
       </c>
@@ -15776,7 +15692,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="24" t="s">
         <v>11</v>
       </c>
@@ -15806,7 +15722,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="24" t="s">
         <v>12</v>
       </c>
@@ -15836,7 +15752,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="24" t="s">
         <v>13</v>
       </c>
@@ -15866,7 +15782,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="24" t="s">
         <v>14</v>
       </c>
@@ -15896,7 +15812,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="24" t="s">
         <v>15</v>
       </c>
@@ -15926,7 +15842,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="24" t="s">
@@ -15958,7 +15874,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="24" t="s">
         <v>9</v>
       </c>
@@ -15988,7 +15904,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="24" t="s">
         <v>10</v>
       </c>
@@ -16018,7 +15934,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="24" t="s">
         <v>11</v>
       </c>
@@ -16048,7 +15964,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="24" t="s">
         <v>12</v>
       </c>
@@ -16078,7 +15994,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="24" t="s">
         <v>13</v>
       </c>
@@ -16108,7 +16024,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="24" t="s">
         <v>14</v>
       </c>
@@ -16138,7 +16054,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="24" t="s">
         <v>15</v>
       </c>
@@ -16168,7 +16084,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
@@ -16200,7 +16116,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="24" t="s">
         <v>9</v>
       </c>
@@ -16230,7 +16146,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="24" t="s">
         <v>10</v>
       </c>
@@ -16260,7 +16176,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="24" t="s">
         <v>11</v>
       </c>
@@ -16290,7 +16206,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="24" t="s">
         <v>12</v>
       </c>
@@ -16320,7 +16236,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="24" t="s">
         <v>13</v>
       </c>
@@ -16350,7 +16266,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="24" t="s">
         <v>14</v>
       </c>
@@ -16380,7 +16296,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="24" t="s">
         <v>15</v>
       </c>
@@ -16410,7 +16326,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="24" t="s">
@@ -16442,7 +16358,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="24" t="s">
         <v>9</v>
       </c>
@@ -16472,7 +16388,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="24" t="s">
         <v>10</v>
       </c>
@@ -16502,7 +16418,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="24" t="s">
         <v>11</v>
       </c>
@@ -16532,7 +16448,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="24" t="s">
         <v>12</v>
       </c>
@@ -16562,7 +16478,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="24" t="s">
         <v>13</v>
       </c>
@@ -16592,7 +16508,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="24" t="s">
         <v>14</v>
       </c>
@@ -16622,7 +16538,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="24" t="s">
         <v>15</v>
       </c>
@@ -16652,7 +16568,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="24" t="s">
@@ -16684,7 +16600,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="24" t="s">
         <v>9</v>
       </c>
@@ -16714,7 +16630,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="24" t="s">
         <v>10</v>
       </c>
@@ -16744,7 +16660,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="24" t="s">
         <v>11</v>
       </c>
@@ -16774,7 +16690,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="24" t="s">
         <v>12</v>
       </c>
@@ -16804,7 +16720,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="24" t="s">
         <v>13</v>
       </c>
@@ -16834,7 +16750,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="24" t="s">
         <v>14</v>
       </c>
@@ -16864,7 +16780,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="24" t="s">
         <v>15</v>
       </c>
@@ -16894,7 +16810,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="24" t="s">
@@ -16926,7 +16842,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="24" t="s">
         <v>9</v>
       </c>
@@ -16956,7 +16872,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="24" t="s">
         <v>10</v>
       </c>
@@ -16986,7 +16902,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="24" t="s">
         <v>11</v>
       </c>
@@ -17016,7 +16932,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="24" t="s">
         <v>12</v>
       </c>
@@ -17046,7 +16962,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="24" t="s">
         <v>13</v>
       </c>
@@ -17076,7 +16992,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="24" t="s">
         <v>14</v>
       </c>
@@ -17106,7 +17022,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="24" t="s">
         <v>15</v>
       </c>
@@ -17136,7 +17052,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="24" t="s">
@@ -17168,7 +17084,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="24" t="s">
         <v>9</v>
       </c>
@@ -17198,7 +17114,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="24" t="s">
         <v>10</v>
       </c>
@@ -17228,7 +17144,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="24" t="s">
         <v>11</v>
       </c>
@@ -17258,7 +17174,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="24" t="s">
         <v>12</v>
       </c>
@@ -17288,7 +17204,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="24" t="s">
         <v>13</v>
       </c>
@@ -17318,7 +17234,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="24" t="s">
         <v>14</v>
       </c>
@@ -17348,7 +17264,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="24" t="s">
         <v>15</v>
       </c>
@@ -17418,17 +17334,17 @@
       <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -17478,7 +17394,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
@@ -17535,7 +17451,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="24" t="s">
         <v>10</v>
       </c>
@@ -17592,7 +17508,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
       </c>
@@ -17649,7 +17565,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
@@ -17706,7 +17622,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="24" t="s">
         <v>13</v>
       </c>
@@ -17763,7 +17679,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="24" t="s">
         <v>14</v>
       </c>
@@ -17820,7 +17736,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="24" t="s">
         <v>15</v>
       </c>
@@ -17877,7 +17793,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="24" t="s">
@@ -17936,7 +17852,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="24" t="s">
         <v>9</v>
       </c>
@@ -17966,7 +17882,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="24" t="s">
         <v>10</v>
       </c>
@@ -17995,7 +17911,7 @@
         <v>2.1633629523645447E-3</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>2</v>
@@ -18017,7 +17933,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="24" t="s">
         <v>11</v>
       </c>
@@ -18046,7 +17962,7 @@
         <v>1.9167549074481146E-3</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K13" s="15">
         <v>0.9</v>
@@ -18068,7 +17984,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
@@ -18097,7 +18013,7 @@
         <v>1.7459291454209641E-3</v>
       </c>
       <c r="J14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K14" s="15">
         <v>2.9</v>
@@ -18119,7 +18035,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="24" t="s">
         <v>13</v>
       </c>
@@ -18149,7 +18065,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="24" t="s">
         <v>14</v>
       </c>
@@ -18179,7 +18095,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="24" t="s">
         <v>15</v>
       </c>
@@ -18209,7 +18125,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="24" t="s">
@@ -18241,7 +18157,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="24" t="s">
         <v>9</v>
       </c>
@@ -18271,7 +18187,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="24" t="s">
         <v>10</v>
       </c>
@@ -18301,7 +18217,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="24" t="s">
         <v>11</v>
       </c>
@@ -18331,7 +18247,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="24" t="s">
         <v>12</v>
       </c>
@@ -18361,7 +18277,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="24" t="s">
         <v>13</v>
       </c>
@@ -18391,7 +18307,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="24" t="s">
         <v>14</v>
       </c>
@@ -18421,7 +18337,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="24" t="s">
         <v>15</v>
       </c>
@@ -18451,7 +18367,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="24" t="s">
@@ -18483,7 +18399,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="24" t="s">
         <v>9</v>
       </c>
@@ -18513,7 +18429,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="24" t="s">
         <v>10</v>
       </c>
@@ -18543,7 +18459,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="24" t="s">
         <v>11</v>
       </c>
@@ -18573,7 +18489,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="24" t="s">
         <v>12</v>
       </c>
@@ -18603,7 +18519,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="24" t="s">
         <v>13</v>
       </c>
@@ -18633,7 +18549,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="24" t="s">
         <v>14</v>
       </c>
@@ -18663,7 +18579,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="24" t="s">
         <v>15</v>
       </c>
@@ -18693,7 +18609,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
@@ -18725,7 +18641,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="24" t="s">
         <v>9</v>
       </c>
@@ -18755,7 +18671,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="24" t="s">
         <v>10</v>
       </c>
@@ -18785,7 +18701,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="24" t="s">
         <v>11</v>
       </c>
@@ -18815,7 +18731,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="24" t="s">
         <v>12</v>
       </c>
@@ -18845,7 +18761,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="24" t="s">
         <v>13</v>
       </c>
@@ -18875,7 +18791,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="24" t="s">
         <v>14</v>
       </c>
@@ -18905,7 +18821,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="24" t="s">
         <v>15</v>
       </c>
@@ -18935,7 +18851,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="24" t="s">
@@ -18967,7 +18883,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="24" t="s">
         <v>9</v>
       </c>
@@ -18997,7 +18913,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="24" t="s">
         <v>10</v>
       </c>
@@ -19027,7 +18943,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="24" t="s">
         <v>11</v>
       </c>
@@ -19057,7 +18973,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="24" t="s">
         <v>12</v>
       </c>
@@ -19087,7 +19003,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="24" t="s">
         <v>13</v>
       </c>
@@ -19117,7 +19033,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="24" t="s">
         <v>14</v>
       </c>
@@ -19147,7 +19063,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="24" t="s">
         <v>15</v>
       </c>
@@ -19177,7 +19093,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B50" s="24" t="s">
@@ -19209,7 +19125,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="24" t="s">
         <v>9</v>
       </c>
@@ -19239,7 +19155,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="24" t="s">
         <v>10</v>
       </c>
@@ -19269,7 +19185,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="24" t="s">
         <v>11</v>
       </c>
@@ -19299,7 +19215,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="24" t="s">
         <v>12</v>
       </c>
@@ -19329,7 +19245,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="24" t="s">
         <v>13</v>
       </c>
@@ -19359,7 +19275,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="24" t="s">
         <v>14</v>
       </c>
@@ -19389,7 +19305,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="24" t="s">
         <v>15</v>
       </c>
@@ -19419,7 +19335,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="24" t="s">
@@ -19451,7 +19367,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="24" t="s">
         <v>9</v>
       </c>
@@ -19481,7 +19397,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="24" t="s">
         <v>10</v>
       </c>
@@ -19511,7 +19427,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="24" t="s">
         <v>11</v>
       </c>
@@ -19541,7 +19457,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="24" t="s">
         <v>12</v>
       </c>
@@ -19571,7 +19487,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="24" t="s">
         <v>13</v>
       </c>
@@ -19601,7 +19517,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="24" t="s">
         <v>14</v>
       </c>
@@ -19631,7 +19547,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="24" t="s">
         <v>15</v>
       </c>
@@ -19661,7 +19577,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="24" t="s">
@@ -19693,7 +19609,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="24" t="s">
         <v>9</v>
       </c>
@@ -19723,7 +19639,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="24" t="s">
         <v>10</v>
       </c>
@@ -19753,7 +19669,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="24" t="s">
         <v>11</v>
       </c>
@@ -19783,7 +19699,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="24" t="s">
         <v>12</v>
       </c>
@@ -19813,7 +19729,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="24" t="s">
         <v>13</v>
       </c>
@@ -19843,7 +19759,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="24" t="s">
         <v>14</v>
       </c>
@@ -19873,7 +19789,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="24" t="s">
         <v>15</v>
       </c>
